--- a/diss/krsnln.xlsx
+++ b/diss/krsnln.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PVT_TSU\diss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B412C45-E13C-4D79-A439-75BBE4A07C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B72ADF-30FF-4248-8678-DC9733397FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>C6</t>
   </si>
@@ -127,9 +127,6 @@
     <t>C35</t>
   </si>
   <si>
-    <t>C36+</t>
-  </si>
-  <si>
     <t>Component</t>
   </si>
   <si>
@@ -170,13 +167,16 @@
   </si>
   <si>
     <t>H2S</t>
+  </si>
+  <si>
+    <t>C36</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +198,23 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -207,7 +224,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -254,11 +271,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -275,6 +307,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -563,15 +602,15 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -580,7 +619,7 @@
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>1.4830000000000001E-2</v>
@@ -589,7 +628,7 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4">
         <v>7.0000000000000007E-5</v>
@@ -598,7 +637,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="4">
         <v>1.0000000000000001E-5</v>
@@ -607,7 +646,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4">
         <v>2.6099999999999999E-3</v>
@@ -616,7 +655,7 @@
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4">
         <v>0.38938</v>
@@ -625,7 +664,7 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="4">
         <v>0.10337999999999999</v>
@@ -634,7 +673,7 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="4">
         <v>7.8710000000000002E-2</v>
@@ -643,7 +682,7 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4">
         <v>9.7800000000000005E-3</v>
@@ -652,7 +691,7 @@
     </row>
     <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="4">
         <v>3.0430000000000002E-2</v>
@@ -661,7 +700,7 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4">
         <v>8.7399999999999995E-3</v>
@@ -670,7 +709,7 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4">
         <v>1.729E-2</v>
@@ -949,7 +988,7 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B44" s="4">
         <v>2.1530000000000001E-2</v>
@@ -964,9 +1003,1491 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB607D19-2929-4A16-85A0-0C9C9A33B84E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AO44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2.6102611422538801E-3</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+    </row>
+    <row r="3" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.48314833641052E-2</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="7"/>
+      <c r="AO3" s="7"/>
+    </row>
+    <row r="4" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.38941894531249999</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="7"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="7"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="7"/>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="7"/>
+      <c r="AN4" s="7"/>
+      <c r="AO4" s="7"/>
+    </row>
+    <row r="5" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.10339034080505399</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="7"/>
+      <c r="AJ5" s="7"/>
+      <c r="AK5" s="7"/>
+      <c r="AL5" s="7"/>
+      <c r="AM5" s="7"/>
+      <c r="AN5" s="7"/>
+      <c r="AO5" s="7"/>
+    </row>
+    <row r="6" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4">
+        <v>7.87178707122803E-2</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="7"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="7"/>
+      <c r="AM6" s="7"/>
+      <c r="AN6" s="7"/>
+      <c r="AO6" s="7"/>
+    </row>
+    <row r="7" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="4">
+        <v>9.7809767723083495E-3</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="7"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
+    </row>
+    <row r="8" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3.0433042049407999E-2</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
+    </row>
+    <row r="9" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="4">
+        <v>8.74087512493134E-3</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="7"/>
+      <c r="AJ9" s="7"/>
+      <c r="AK9" s="7"/>
+      <c r="AL9" s="7"/>
+      <c r="AM9" s="7"/>
+      <c r="AN9" s="7"/>
+      <c r="AO9" s="7"/>
+    </row>
+    <row r="10" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.72917282581329E-2</v>
+      </c>
+      <c r="N10" s="6"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="7"/>
+      <c r="AJ10" s="7"/>
+      <c r="AK10" s="7"/>
+      <c r="AL10" s="7"/>
+      <c r="AM10" s="7"/>
+      <c r="AN10" s="7"/>
+      <c r="AO10" s="7"/>
+    </row>
+    <row r="11" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2.2392239570617697E-2</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="7"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
+      <c r="AO11" s="7"/>
+    </row>
+    <row r="12" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3.20032024383545E-2</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="7"/>
+      <c r="AM12" s="7"/>
+      <c r="AN12" s="7"/>
+      <c r="AO12" s="7"/>
+    </row>
+    <row r="13" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>4.0134010314941397E-2</v>
+      </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="7"/>
+      <c r="AJ13" s="7"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="7"/>
+      <c r="AM13" s="7"/>
+      <c r="AN13" s="7"/>
+      <c r="AO13" s="7"/>
+    </row>
+    <row r="14" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2.9442944526672399E-2</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="7"/>
+      <c r="AJ14" s="7"/>
+      <c r="AK14" s="7"/>
+      <c r="AL14" s="7"/>
+      <c r="AM14" s="7"/>
+      <c r="AN14" s="7"/>
+      <c r="AO14" s="7"/>
+    </row>
+    <row r="15" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2.5342533588409401E-2</v>
+      </c>
+      <c r="N15" s="6"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+    </row>
+    <row r="16" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2.0472047328949E-2</v>
+      </c>
+      <c r="N16" s="6"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="7"/>
+      <c r="AN16" s="7"/>
+      <c r="AO16" s="7"/>
+    </row>
+    <row r="17" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1.7351735830307E-2</v>
+      </c>
+      <c r="N17" s="6"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="7"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="7"/>
+      <c r="AI17" s="7"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="7"/>
+      <c r="AL17" s="7"/>
+      <c r="AM17" s="7"/>
+      <c r="AN17" s="7"/>
+      <c r="AO17" s="7"/>
+    </row>
+    <row r="18" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1.6791678667068499E-2</v>
+      </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="7"/>
+      <c r="AM18" s="7"/>
+      <c r="AN18" s="7"/>
+      <c r="AO18" s="7"/>
+    </row>
+    <row r="19" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1.47614753246307E-2</v>
+      </c>
+      <c r="N19" s="6"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7"/>
+      <c r="AH19" s="7"/>
+      <c r="AI19" s="7"/>
+      <c r="AJ19" s="7"/>
+      <c r="AK19" s="7"/>
+      <c r="AL19" s="7"/>
+      <c r="AM19" s="7"/>
+      <c r="AN19" s="7"/>
+      <c r="AO19" s="7"/>
+    </row>
+    <row r="20" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1.21512150764465E-2</v>
+      </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="7"/>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="7"/>
+      <c r="AI20" s="7"/>
+      <c r="AJ20" s="7"/>
+      <c r="AK20" s="7"/>
+      <c r="AL20" s="7"/>
+      <c r="AM20" s="7"/>
+      <c r="AN20" s="7"/>
+      <c r="AO20" s="7"/>
+    </row>
+    <row r="21" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="4">
+        <v>1.0651066303253201E-2</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7"/>
+      <c r="AA21" s="7"/>
+      <c r="AB21" s="7"/>
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="7"/>
+      <c r="AE21" s="7"/>
+      <c r="AF21" s="7"/>
+      <c r="AG21" s="7"/>
+      <c r="AH21" s="7"/>
+      <c r="AI21" s="7"/>
+      <c r="AJ21" s="7"/>
+      <c r="AK21" s="7"/>
+      <c r="AL21" s="7"/>
+      <c r="AM21" s="7"/>
+      <c r="AN21" s="7"/>
+      <c r="AO21" s="7"/>
+    </row>
+    <row r="22" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="4">
+        <v>9.0409040451049812E-3</v>
+      </c>
+      <c r="N22" s="6"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
+      <c r="AA22" s="7"/>
+      <c r="AB22" s="7"/>
+      <c r="AC22" s="7"/>
+      <c r="AD22" s="7"/>
+      <c r="AE22" s="7"/>
+      <c r="AF22" s="7"/>
+      <c r="AG22" s="7"/>
+      <c r="AH22" s="7"/>
+      <c r="AI22" s="7"/>
+      <c r="AJ22" s="7"/>
+      <c r="AK22" s="7"/>
+      <c r="AL22" s="7"/>
+      <c r="AM22" s="7"/>
+      <c r="AN22" s="7"/>
+      <c r="AO22" s="7"/>
+    </row>
+    <row r="23" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="4">
+        <v>8.5708570480346694E-3</v>
+      </c>
+      <c r="N23" s="6"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="7"/>
+      <c r="AG23" s="7"/>
+      <c r="AH23" s="7"/>
+      <c r="AI23" s="7"/>
+      <c r="AJ23" s="7"/>
+      <c r="AK23" s="7"/>
+      <c r="AL23" s="7"/>
+      <c r="AM23" s="7"/>
+      <c r="AN23" s="7"/>
+      <c r="AO23" s="7"/>
+    </row>
+    <row r="24" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="4">
+        <v>8.0008006095886198E-3</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="7"/>
+      <c r="AG24" s="7"/>
+      <c r="AH24" s="7"/>
+      <c r="AI24" s="7"/>
+      <c r="AJ24" s="7"/>
+      <c r="AK24" s="7"/>
+      <c r="AL24" s="7"/>
+      <c r="AM24" s="7"/>
+      <c r="AN24" s="7"/>
+      <c r="AO24" s="7"/>
+    </row>
+    <row r="25" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="4">
+        <v>6.88068866729736E-3</v>
+      </c>
+      <c r="N25" s="6"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="7"/>
+      <c r="AF25" s="7"/>
+      <c r="AG25" s="7"/>
+      <c r="AH25" s="7"/>
+      <c r="AI25" s="7"/>
+      <c r="AJ25" s="7"/>
+      <c r="AK25" s="7"/>
+      <c r="AL25" s="7"/>
+      <c r="AM25" s="7"/>
+      <c r="AN25" s="7"/>
+      <c r="AO25" s="7"/>
+    </row>
+    <row r="26" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="4">
+        <v>5.6905692815780598E-3</v>
+      </c>
+      <c r="N26" s="6"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
+      <c r="AC26" s="7"/>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="7"/>
+      <c r="AF26" s="7"/>
+      <c r="AG26" s="7"/>
+      <c r="AH26" s="7"/>
+      <c r="AI26" s="7"/>
+      <c r="AJ26" s="7"/>
+      <c r="AK26" s="7"/>
+      <c r="AL26" s="7"/>
+      <c r="AM26" s="7"/>
+      <c r="AN26" s="7"/>
+      <c r="AO26" s="7"/>
+    </row>
+    <row r="27" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4">
+        <v>5.1305133104324295E-3</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="7"/>
+      <c r="AA27" s="7"/>
+      <c r="AB27" s="7"/>
+      <c r="AC27" s="7"/>
+      <c r="AD27" s="7"/>
+      <c r="AE27" s="7"/>
+      <c r="AF27" s="7"/>
+      <c r="AG27" s="7"/>
+      <c r="AH27" s="7"/>
+      <c r="AI27" s="7"/>
+      <c r="AJ27" s="7"/>
+      <c r="AK27" s="7"/>
+      <c r="AL27" s="7"/>
+      <c r="AM27" s="7"/>
+      <c r="AN27" s="7"/>
+      <c r="AO27" s="7"/>
+    </row>
+    <row r="28" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="4">
+        <v>4.8604857921600297E-3</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="7"/>
+      <c r="AA28" s="7"/>
+      <c r="AB28" s="7"/>
+      <c r="AC28" s="7"/>
+      <c r="AD28" s="7"/>
+      <c r="AE28" s="7"/>
+      <c r="AF28" s="7"/>
+      <c r="AG28" s="7"/>
+      <c r="AH28" s="7"/>
+      <c r="AI28" s="7"/>
+      <c r="AJ28" s="7"/>
+      <c r="AK28" s="7"/>
+      <c r="AL28" s="7"/>
+      <c r="AM28" s="7"/>
+      <c r="AN28" s="7"/>
+      <c r="AO28" s="7"/>
+    </row>
+    <row r="29" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="4">
+        <v>4.4504451751709003E-3</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="7"/>
+      <c r="AA29" s="7"/>
+      <c r="AB29" s="7"/>
+      <c r="AC29" s="7"/>
+      <c r="AD29" s="7"/>
+      <c r="AE29" s="7"/>
+      <c r="AF29" s="7"/>
+      <c r="AG29" s="7"/>
+      <c r="AH29" s="7"/>
+      <c r="AI29" s="7"/>
+      <c r="AJ29" s="7"/>
+      <c r="AK29" s="7"/>
+      <c r="AL29" s="7"/>
+      <c r="AM29" s="7"/>
+      <c r="AN29" s="7"/>
+      <c r="AO29" s="7"/>
+    </row>
+    <row r="30" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="4">
+        <v>3.9103910326957706E-3</v>
+      </c>
+      <c r="N30" s="6"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="7"/>
+      <c r="AB30" s="7"/>
+      <c r="AC30" s="7"/>
+      <c r="AD30" s="7"/>
+      <c r="AE30" s="7"/>
+      <c r="AF30" s="7"/>
+      <c r="AG30" s="7"/>
+      <c r="AH30" s="7"/>
+      <c r="AI30" s="7"/>
+      <c r="AJ30" s="7"/>
+      <c r="AK30" s="7"/>
+      <c r="AL30" s="7"/>
+      <c r="AM30" s="7"/>
+      <c r="AN30" s="7"/>
+      <c r="AO30" s="7"/>
+    </row>
+    <row r="31" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="4">
+        <v>3.6303630471229598E-3</v>
+      </c>
+      <c r="N31" s="6"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="7"/>
+      <c r="AA31" s="7"/>
+      <c r="AB31" s="7"/>
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="7"/>
+      <c r="AE31" s="7"/>
+      <c r="AF31" s="7"/>
+      <c r="AG31" s="7"/>
+      <c r="AH31" s="7"/>
+      <c r="AI31" s="7"/>
+      <c r="AJ31" s="7"/>
+      <c r="AK31" s="7"/>
+      <c r="AL31" s="7"/>
+      <c r="AM31" s="7"/>
+      <c r="AN31" s="7"/>
+      <c r="AO31" s="7"/>
+    </row>
+    <row r="32" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="4">
+        <v>3.48034799098969E-3</v>
+      </c>
+      <c r="N32" s="6"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
+      <c r="Y32" s="7"/>
+      <c r="Z32" s="7"/>
+      <c r="AA32" s="7"/>
+      <c r="AB32" s="7"/>
+      <c r="AC32" s="7"/>
+      <c r="AD32" s="7"/>
+      <c r="AE32" s="7"/>
+      <c r="AF32" s="7"/>
+      <c r="AG32" s="7"/>
+      <c r="AH32" s="7"/>
+      <c r="AI32" s="7"/>
+      <c r="AJ32" s="7"/>
+      <c r="AK32" s="7"/>
+      <c r="AL32" s="7"/>
+      <c r="AM32" s="7"/>
+      <c r="AN32" s="7"/>
+      <c r="AO32" s="7"/>
+    </row>
+    <row r="33" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2.7502751350402797E-3</v>
+      </c>
+      <c r="N33" s="6"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="7"/>
+      <c r="AE33" s="7"/>
+      <c r="AF33" s="7"/>
+      <c r="AG33" s="7"/>
+      <c r="AH33" s="7"/>
+      <c r="AI33" s="7"/>
+      <c r="AJ33" s="7"/>
+      <c r="AK33" s="7"/>
+      <c r="AL33" s="7"/>
+      <c r="AM33" s="7"/>
+      <c r="AN33" s="7"/>
+      <c r="AO33" s="7"/>
+    </row>
+    <row r="34" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2.8902891278266901E-3</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
+      <c r="AA34" s="7"/>
+      <c r="AB34" s="7"/>
+      <c r="AC34" s="7"/>
+      <c r="AD34" s="7"/>
+      <c r="AE34" s="7"/>
+      <c r="AF34" s="7"/>
+      <c r="AG34" s="7"/>
+      <c r="AH34" s="7"/>
+      <c r="AI34" s="7"/>
+      <c r="AJ34" s="7"/>
+      <c r="AK34" s="7"/>
+      <c r="AL34" s="7"/>
+      <c r="AM34" s="7"/>
+      <c r="AN34" s="7"/>
+      <c r="AO34" s="7"/>
+    </row>
+    <row r="35" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="4">
+        <v>2.6602661609649702E-3</v>
+      </c>
+      <c r="N35" s="6"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+      <c r="AC35" s="7"/>
+      <c r="AD35" s="7"/>
+      <c r="AE35" s="7"/>
+      <c r="AF35" s="7"/>
+      <c r="AG35" s="7"/>
+      <c r="AH35" s="7"/>
+      <c r="AI35" s="7"/>
+      <c r="AJ35" s="7"/>
+      <c r="AK35" s="7"/>
+      <c r="AL35" s="7"/>
+      <c r="AM35" s="7"/>
+      <c r="AN35" s="7"/>
+      <c r="AO35" s="7"/>
+    </row>
+    <row r="36" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="4">
+        <v>2.4102412164211302E-3</v>
+      </c>
+      <c r="N36" s="6"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="7"/>
+      <c r="AA36" s="7"/>
+      <c r="AB36" s="7"/>
+      <c r="AC36" s="7"/>
+      <c r="AD36" s="7"/>
+      <c r="AE36" s="7"/>
+      <c r="AF36" s="7"/>
+      <c r="AG36" s="7"/>
+      <c r="AH36" s="7"/>
+      <c r="AI36" s="7"/>
+      <c r="AJ36" s="7"/>
+      <c r="AK36" s="7"/>
+      <c r="AL36" s="7"/>
+      <c r="AM36" s="7"/>
+      <c r="AN36" s="7"/>
+      <c r="AO36" s="7"/>
+    </row>
+    <row r="37" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="4">
+        <v>2.1102112531662001E-3</v>
+      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
+      <c r="AC37" s="7"/>
+      <c r="AD37" s="7"/>
+      <c r="AE37" s="7"/>
+      <c r="AF37" s="7"/>
+      <c r="AG37" s="7"/>
+      <c r="AH37" s="7"/>
+      <c r="AI37" s="7"/>
+      <c r="AJ37" s="7"/>
+      <c r="AK37" s="7"/>
+      <c r="AL37" s="7"/>
+      <c r="AM37" s="7"/>
+      <c r="AN37" s="7"/>
+      <c r="AO37" s="7"/>
+    </row>
+    <row r="38" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="4">
+        <v>1.8301829695701599E-3</v>
+      </c>
+      <c r="N38" s="6"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
+      <c r="Y38" s="7"/>
+      <c r="Z38" s="7"/>
+      <c r="AA38" s="7"/>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7"/>
+      <c r="AD38" s="7"/>
+      <c r="AE38" s="7"/>
+      <c r="AF38" s="7"/>
+      <c r="AG38" s="7"/>
+      <c r="AH38" s="7"/>
+      <c r="AI38" s="7"/>
+      <c r="AJ38" s="7"/>
+      <c r="AK38" s="7"/>
+      <c r="AL38" s="7"/>
+      <c r="AM38" s="7"/>
+      <c r="AN38" s="7"/>
+      <c r="AO38" s="7"/>
+    </row>
+    <row r="39" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1.7001700401306199E-3</v>
+      </c>
+      <c r="N39" s="6"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="7"/>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="7"/>
+      <c r="AE39" s="7"/>
+      <c r="AF39" s="7"/>
+      <c r="AG39" s="7"/>
+      <c r="AH39" s="7"/>
+      <c r="AI39" s="7"/>
+      <c r="AJ39" s="7"/>
+      <c r="AK39" s="7"/>
+      <c r="AL39" s="7"/>
+      <c r="AM39" s="7"/>
+      <c r="AN39" s="7"/>
+      <c r="AO39" s="7"/>
+    </row>
+    <row r="40" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1.76017612218857E-3</v>
+      </c>
+      <c r="N40" s="6"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
+      <c r="AA40" s="7"/>
+      <c r="AB40" s="7"/>
+      <c r="AC40" s="7"/>
+      <c r="AD40" s="7"/>
+      <c r="AE40" s="7"/>
+      <c r="AF40" s="7"/>
+      <c r="AG40" s="7"/>
+      <c r="AH40" s="7"/>
+      <c r="AI40" s="7"/>
+      <c r="AJ40" s="7"/>
+      <c r="AK40" s="7"/>
+      <c r="AL40" s="7"/>
+      <c r="AM40" s="7"/>
+      <c r="AN40" s="7"/>
+      <c r="AO40" s="7"/>
+    </row>
+    <row r="41" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="4">
+        <v>2.1532154083252E-2</v>
+      </c>
+      <c r="N41" s="6"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+      <c r="AC41" s="7"/>
+      <c r="AD41" s="7"/>
+      <c r="AE41" s="7"/>
+      <c r="AF41" s="7"/>
+      <c r="AG41" s="7"/>
+      <c r="AH41" s="7"/>
+      <c r="AI41" s="7"/>
+      <c r="AJ41" s="7"/>
+      <c r="AK41" s="7"/>
+      <c r="AL41" s="7"/>
+      <c r="AM41" s="7"/>
+      <c r="AN41" s="7"/>
+      <c r="AO41" s="7"/>
+    </row>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="N42" s="6"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+      <c r="AA42" s="7"/>
+      <c r="AB42" s="7"/>
+      <c r="AC42" s="7"/>
+      <c r="AD42" s="7"/>
+      <c r="AE42" s="7"/>
+      <c r="AF42" s="7"/>
+      <c r="AG42" s="7"/>
+      <c r="AH42" s="7"/>
+      <c r="AI42" s="7"/>
+      <c r="AJ42" s="7"/>
+      <c r="AK42" s="7"/>
+      <c r="AL42" s="7"/>
+      <c r="AM42" s="7"/>
+      <c r="AN42" s="7"/>
+      <c r="AO42" s="7"/>
+    </row>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="T44" s="8"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>